--- a/data/GBD_diseases.xlsx
+++ b/data/GBD_diseases.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E73CFF-317F-FE44-A127-071B7B806460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83D7863-C27C-1F48-9F3D-805C6D2B18A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31340" yWindow="-1600" windowWidth="27240" windowHeight="15100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
+    <workbookView xWindow="31500" yWindow="-1380" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
     <sheet name="Lower" sheetId="2" r:id="rId2"/>
     <sheet name="Upper" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="24">
   <si>
     <t>Male</t>
   </si>
@@ -100,9 +100,6 @@
     <t>cvd_incidence</t>
   </si>
   <si>
-    <t>bc_incidence</t>
-  </si>
-  <si>
     <t>dem_incidence</t>
   </si>
   <si>
@@ -112,43 +109,7 @@
     <t>pop_age_grp</t>
   </si>
   <si>
-    <t>age_grp.x</t>
-  </si>
-  <si>
-    <t>dem_incidence_low</t>
-  </si>
-  <si>
-    <t>bc_incidence_up</t>
-  </si>
-  <si>
-    <t>bc_incidence_low</t>
-  </si>
-  <si>
-    <t>cvd_incidence_low</t>
-  </si>
-  <si>
-    <t>diab2_incidence_low</t>
-  </si>
-  <si>
-    <t>cancer_incidence_low</t>
-  </si>
-  <si>
-    <t>dep_incidence_low</t>
-  </si>
-  <si>
-    <t>dem_incidence_up</t>
-  </si>
-  <si>
-    <t>cvd_incidence_up</t>
-  </si>
-  <si>
-    <t>diab2_incidence_up</t>
-  </si>
-  <si>
-    <t>cancer_incidence_up</t>
-  </si>
-  <si>
-    <t>dep_incidence_up</t>
+    <t>age_grp</t>
   </si>
 </sst>
 </file>
@@ -529,39 +490,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD0F75B-B6CB-6D48-ABCA-C0DE307A97B8}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
       <c r="H1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -571,26 +536,23 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1">
-        <v>0</v>
+      <c r="D2" s="2">
+        <v>470.69469038044798</v>
       </c>
       <c r="E2" s="1">
-        <v>46.985244064993502</v>
-      </c>
-      <c r="F2" s="2">
-        <v>470.69469038044798</v>
+        <v>31895.028700513602</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1820.60209060134</v>
       </c>
       <c r="G2" s="1">
-        <v>1820.60209060134</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>31895.028700513602</v>
-      </c>
-      <c r="I2" s="1">
         <v>110106.980466972</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -600,26 +562,23 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
+      <c r="D3" s="2">
+        <v>632.77539815350804</v>
       </c>
       <c r="E3" s="1">
-        <v>262.93937582697203</v>
-      </c>
-      <c r="F3" s="2">
-        <v>632.77539815350804</v>
+        <v>41373.529924294002</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2169.7299767801601</v>
       </c>
       <c r="G3" s="1">
-        <v>2169.7299767801601</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>41373.529924294002</v>
-      </c>
-      <c r="I3" s="1">
         <v>109941.189467854</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -629,26 +588,23 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1">
-        <v>0</v>
+      <c r="D4" s="2">
+        <v>940.43433537620399</v>
       </c>
       <c r="E4" s="1">
-        <v>910.86506240088602</v>
-      </c>
-      <c r="F4" s="2">
-        <v>940.43433537620399</v>
+        <v>54827.829429694502</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2650.1162851320801</v>
       </c>
       <c r="G4" s="1">
-        <v>2650.1162851320801</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>54827.829429694502</v>
-      </c>
-      <c r="I4" s="1">
         <v>115456.646754588</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -658,26 +614,23 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1">
-        <v>0</v>
+      <c r="D5" s="2">
+        <v>1349.06519303611</v>
       </c>
       <c r="E5" s="1">
-        <v>1869.5575392528101</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1349.06519303611</v>
+        <v>67646.912270110799</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3193.72590896884</v>
       </c>
       <c r="G5" s="1">
-        <v>3193.72590896884</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>67646.912270110799</v>
-      </c>
-      <c r="I5" s="1">
         <v>117815.618668783</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -687,26 +640,23 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
+        <v>3101.65917634979</v>
+      </c>
+      <c r="E6" s="1">
+        <v>78426.804447342205</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3757.3592830689499</v>
+      </c>
+      <c r="G6" s="1">
         <v>200.45055222268201</v>
       </c>
-      <c r="E6" s="1">
-        <v>3605.9935562933301</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3101.65917634979</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3757.3592830689499</v>
-      </c>
       <c r="H6" s="1">
-        <v>78426.804447342205</v>
-      </c>
-      <c r="I6" s="1">
         <v>117181.94292290301</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -716,26 +666,23 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
+        <v>5221.7732342678501</v>
+      </c>
+      <c r="E7" s="1">
+        <v>94599.433891750406</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4734.0420195553697</v>
+      </c>
+      <c r="G7" s="1">
         <v>579.92204176205803</v>
       </c>
-      <c r="E7" s="1">
-        <v>5662.1815927131001</v>
-      </c>
-      <c r="F7" s="2">
-        <v>5221.7732342678501</v>
-      </c>
-      <c r="G7" s="1">
-        <v>4734.0420195553697</v>
-      </c>
       <c r="H7" s="1">
-        <v>94599.433891750406</v>
-      </c>
-      <c r="I7" s="1">
         <v>124337.67221672799</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -745,26 +692,23 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
+        <v>8374.8103610041799</v>
+      </c>
+      <c r="E8" s="1">
+        <v>101403.734074696</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6858.1379876118799</v>
+      </c>
+      <c r="G8" s="1">
         <v>713.40720180574601</v>
       </c>
-      <c r="E8" s="1">
-        <v>6467.0407539628004</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8374.8103610041799</v>
-      </c>
-      <c r="G8" s="1">
-        <v>6858.1379876118799</v>
-      </c>
       <c r="H8" s="1">
-        <v>101403.734074696</v>
-      </c>
-      <c r="I8" s="1">
         <v>124548.53842968799</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -774,26 +718,23 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
+        <v>12430.148542774999</v>
+      </c>
+      <c r="E9" s="1">
+        <v>105611.803169869</v>
+      </c>
+      <c r="F9" s="1">
+        <v>10022.503228932601</v>
+      </c>
+      <c r="G9" s="1">
         <v>898.23776155674796</v>
       </c>
-      <c r="E9" s="1">
-        <v>6677.6200249973599</v>
-      </c>
-      <c r="F9" s="2">
-        <v>12430.148542774999</v>
-      </c>
-      <c r="G9" s="1">
-        <v>10022.503228932601</v>
-      </c>
       <c r="H9" s="1">
-        <v>105611.803169869</v>
-      </c>
-      <c r="I9" s="1">
         <v>121389.983337382</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -803,26 +744,23 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
+        <v>20587.442224745701</v>
+      </c>
+      <c r="E10" s="1">
+        <v>101256.038155812</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10803.393482634399</v>
+      </c>
+      <c r="G10" s="1">
         <v>2072.6209123938602</v>
       </c>
-      <c r="E10" s="1">
-        <v>7493.3171621217898</v>
-      </c>
-      <c r="F10" s="2">
-        <v>20587.442224745701</v>
-      </c>
-      <c r="G10" s="1">
-        <v>10803.393482634399</v>
-      </c>
       <c r="H10" s="1">
-        <v>101256.038155812</v>
-      </c>
-      <c r="I10" s="1">
         <v>117939.92514770701</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -832,26 +770,23 @@
       <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
+        <v>32657.341173983099</v>
+      </c>
+      <c r="E11" s="1">
+        <v>91242.370890545499</v>
+      </c>
+      <c r="F11" s="1">
+        <v>9873.4820198206107</v>
+      </c>
+      <c r="G11" s="1">
         <v>5605.3712666789497</v>
       </c>
-      <c r="E11" s="1">
-        <v>8129.2998451592402</v>
-      </c>
-      <c r="F11" s="2">
-        <v>32657.341173983099</v>
-      </c>
-      <c r="G11" s="1">
-        <v>9873.4820198206107</v>
-      </c>
       <c r="H11" s="1">
-        <v>91242.370890545499</v>
-      </c>
-      <c r="I11" s="1">
         <v>117025.30046122101</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -861,26 +796,23 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
+        <v>37338.508895075996</v>
+      </c>
+      <c r="E12" s="1">
+        <v>70323.291408803503</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5928.3316071394702</v>
+      </c>
+      <c r="G12" s="1">
         <v>9543.1648218351602</v>
       </c>
-      <c r="E12" s="1">
-        <v>7197.55395485193</v>
-      </c>
-      <c r="F12" s="2">
-        <v>37338.508895075996</v>
-      </c>
-      <c r="G12" s="1">
-        <v>5928.3316071394702</v>
-      </c>
       <c r="H12" s="1">
-        <v>70323.291408803503</v>
-      </c>
-      <c r="I12" s="1">
         <v>96232.371325058106</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -890,26 +822,23 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
+        <v>35467.572533225699</v>
+      </c>
+      <c r="E13" s="1">
+        <v>45409.990592704802</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1758.9273243308801</v>
+      </c>
+      <c r="G13" s="1">
         <v>12999.2391768621</v>
       </c>
-      <c r="E13" s="1">
-        <v>4805.9454763048898</v>
-      </c>
-      <c r="F13" s="2">
-        <v>35467.572533225699</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1758.9273243308801</v>
-      </c>
       <c r="H13" s="1">
-        <v>45409.990592704802</v>
-      </c>
-      <c r="I13" s="1">
         <v>71576.162778811806</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -919,26 +848,23 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2">
+        <v>40843.165995684503</v>
+      </c>
+      <c r="E14" s="1">
+        <v>40071.020130189499</v>
+      </c>
+      <c r="F14" s="1">
+        <v>380.459165983319</v>
+      </c>
+      <c r="G14" s="1">
         <v>20835.983559038701</v>
       </c>
-      <c r="E14" s="1">
-        <v>4703.9879333736098</v>
-      </c>
-      <c r="F14" s="2">
-        <v>40843.165995684503</v>
-      </c>
-      <c r="G14" s="1">
-        <v>380.459165983319</v>
-      </c>
       <c r="H14" s="1">
-        <v>40071.020130189499</v>
-      </c>
-      <c r="I14" s="1">
         <v>65942.646528924204</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -948,26 +874,23 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2">
+        <v>39393.748689389802</v>
+      </c>
+      <c r="E15" s="1">
+        <v>30087.313673168901</v>
+      </c>
+      <c r="F15" s="1">
+        <v>167.01273980801099</v>
+      </c>
+      <c r="G15" s="1">
         <v>23167.833796081701</v>
       </c>
-      <c r="E15" s="1">
-        <v>3964.1039772608001</v>
-      </c>
-      <c r="F15" s="2">
-        <v>39393.748689389802</v>
-      </c>
-      <c r="G15" s="1">
-        <v>167.01273980801099</v>
-      </c>
       <c r="H15" s="1">
-        <v>30087.313673168901</v>
-      </c>
-      <c r="I15" s="1">
         <v>51323.210853908997</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -977,26 +900,23 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="D16" s="2">
         <v>979.590678637667</v>
       </c>
+      <c r="E16" s="1">
+        <v>10547.1055404502</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2773.2923883325602</v>
+      </c>
       <c r="G16" s="1">
-        <v>2773.2923883325602</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>10547.1055404502</v>
-      </c>
-      <c r="I16" s="1">
         <v>63725.650599513603</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1006,26 +926,23 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="D17" s="2">
         <v>1201.93972038215</v>
       </c>
+      <c r="E17" s="1">
+        <v>11796.8720129139</v>
+      </c>
+      <c r="F17" s="1">
+        <v>3374.0731419662402</v>
+      </c>
       <c r="G17" s="1">
-        <v>3374.0731419662402</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>11796.8720129139</v>
-      </c>
-      <c r="I17" s="1">
         <v>61953.617402941702</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1035,26 +952,23 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="D18" s="2">
         <v>1854.4928007996</v>
       </c>
+      <c r="E18" s="1">
+        <v>15570.378567695199</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4659.5681303445999</v>
+      </c>
       <c r="G18" s="1">
-        <v>4659.5681303445999</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>15570.378567695199</v>
-      </c>
-      <c r="I18" s="1">
         <v>63951.726487806802</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1064,26 +978,23 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="D19" s="2">
         <v>2911.6926748257501</v>
       </c>
+      <c r="E19" s="1">
+        <v>19831.435365161298</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6242.1614464206496</v>
+      </c>
       <c r="G19" s="1">
-        <v>6242.1614464206496</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>19831.435365161298</v>
-      </c>
-      <c r="I19" s="1">
         <v>65499.398155419098</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1093,26 +1004,23 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="2">
+        <v>5659.6219309011904</v>
+      </c>
+      <c r="E20" s="1">
+        <v>25267.382254248801</v>
+      </c>
+      <c r="F20" s="1">
+        <v>7473.8461896226499</v>
+      </c>
+      <c r="G20" s="1">
         <v>179.37030847911001</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>5659.6219309011904</v>
-      </c>
-      <c r="G20" s="1">
-        <v>7473.8461896226499</v>
-      </c>
       <c r="H20" s="1">
-        <v>25267.382254248801</v>
-      </c>
-      <c r="I20" s="1">
         <v>65091.9510618442</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1122,26 +1030,23 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
+        <v>9575.0456011774895</v>
+      </c>
+      <c r="E21" s="1">
+        <v>36274.301361196303</v>
+      </c>
+      <c r="F21" s="1">
+        <v>8962.2641997762894</v>
+      </c>
+      <c r="G21" s="1">
         <v>512.98459175131802</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9575.0456011774895</v>
-      </c>
-      <c r="G21" s="1">
-        <v>8962.2641997762894</v>
-      </c>
       <c r="H21" s="1">
-        <v>36274.301361196303</v>
-      </c>
-      <c r="I21" s="1">
         <v>67565.817499864803</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1151,26 +1056,23 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="2">
+        <v>15463.018047597399</v>
+      </c>
+      <c r="E22" s="1">
+        <v>47480.353174948003</v>
+      </c>
+      <c r="F22" s="1">
+        <v>10952.9360535551</v>
+      </c>
+      <c r="G22" s="1">
         <v>608.76121231193997</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>15463.018047597399</v>
-      </c>
-      <c r="G22" s="1">
-        <v>10952.9360535551</v>
-      </c>
       <c r="H22" s="1">
-        <v>47480.353174948003</v>
-      </c>
-      <c r="I22" s="1">
         <v>65314.3905427461</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1180,26 +1082,23 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="2">
+        <v>22944.7611337993</v>
+      </c>
+      <c r="E23" s="1">
+        <v>62358.169072636701</v>
+      </c>
+      <c r="F23" s="1">
+        <v>13488.6125537559</v>
+      </c>
+      <c r="G23" s="1">
         <v>799.52407369711796</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>22944.7611337993</v>
-      </c>
-      <c r="G23" s="1">
-        <v>13488.6125537559</v>
-      </c>
       <c r="H23" s="1">
-        <v>62358.169072636701</v>
-      </c>
-      <c r="I23" s="1">
         <v>61507.848943434699</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1209,26 +1108,23 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="2">
+        <v>34012.705162054197</v>
+      </c>
+      <c r="E24" s="1">
+        <v>76354.694622921394</v>
+      </c>
+      <c r="F24" s="1">
+        <v>12523.905111943001</v>
+      </c>
+      <c r="G24" s="1">
         <v>1937.18755936714</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2">
-        <v>34012.705162054197</v>
-      </c>
-      <c r="G24" s="1">
-        <v>12523.905111943001</v>
-      </c>
       <c r="H24" s="1">
-        <v>76354.694622921394</v>
-      </c>
-      <c r="I24" s="1">
         <v>57097.117568491303</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1238,26 +1134,23 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="2">
+        <v>49162.048989562601</v>
+      </c>
+      <c r="E25" s="1">
+        <v>86867.783459435304</v>
+      </c>
+      <c r="F25" s="1">
+        <v>9641.3463135489092</v>
+      </c>
+      <c r="G25" s="1">
         <v>4766.2133119480304</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>49162.048989562601</v>
-      </c>
-      <c r="G25" s="1">
-        <v>9641.3463135489092</v>
-      </c>
       <c r="H25" s="1">
-        <v>86867.783459435304</v>
-      </c>
-      <c r="I25" s="1">
         <v>54760.295815320802</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1267,26 +1160,23 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="2">
+        <v>48399.188138501297</v>
+      </c>
+      <c r="E26" s="1">
+        <v>78052.987440609199</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5121.7042037784004</v>
+      </c>
+      <c r="G26" s="1">
         <v>7503.2825109897203</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <v>48399.188138501297</v>
-      </c>
-      <c r="G26" s="1">
-        <v>5121.7042037784004</v>
-      </c>
       <c r="H26" s="1">
-        <v>78052.987440609199</v>
-      </c>
-      <c r="I26" s="1">
         <v>43206.315763751198</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1296,26 +1186,23 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="2">
+        <v>36791.664427351898</v>
+      </c>
+      <c r="E27" s="1">
+        <v>51419.864913194702</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1331.2874336208299</v>
+      </c>
+      <c r="G27" s="1">
         <v>8917.9373916232998</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
-        <v>36791.664427351898</v>
-      </c>
-      <c r="G27" s="1">
-        <v>1331.2874336208299</v>
-      </c>
       <c r="H27" s="1">
-        <v>51419.864913194702</v>
-      </c>
-      <c r="I27" s="1">
         <v>29283.088765753499</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -1325,26 +1212,23 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="2">
+        <v>34848.668941745302</v>
+      </c>
+      <c r="E28" s="1">
+        <v>40352.991684315602</v>
+      </c>
+      <c r="F28" s="1">
+        <v>193.27290625277899</v>
+      </c>
+      <c r="G28" s="1">
         <v>12279.956847609799</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
-        <v>34848.668941745302</v>
-      </c>
-      <c r="G28" s="1">
-        <v>193.27290625277899</v>
-      </c>
       <c r="H28" s="1">
-        <v>40352.991684315602</v>
-      </c>
-      <c r="I28" s="1">
         <v>22967.3339007953</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -1354,22 +1238,19 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="2">
+        <v>27231.105850723201</v>
+      </c>
+      <c r="E29" s="1">
+        <v>25958.0931464733</v>
+      </c>
+      <c r="F29" s="1">
+        <v>67.897980072262897</v>
+      </c>
+      <c r="G29" s="1">
         <v>11516.040906820101</v>
       </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>27231.105850723201</v>
-      </c>
-      <c r="G29" s="1">
-        <v>67.897980072262897</v>
-      </c>
       <c r="H29" s="1">
-        <v>25958.0931464733</v>
-      </c>
-      <c r="I29" s="1">
         <v>14170.4127573039</v>
       </c>
     </row>
@@ -1380,42 +1261,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E002562B-DD6F-164B-BC33-738F7B5F11A1}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="9" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1425,8 +1307,23 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D2" s="1">
+        <v>355.32041082233798</v>
+      </c>
+      <c r="E2" s="1">
+        <v>20535.585789194702</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1205.6450211404399</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>90350.229755512599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1436,8 +1333,23 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D3" s="1">
+        <v>471.21227118233702</v>
+      </c>
+      <c r="E3" s="1">
+        <v>24199.264253060501</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1478.0992456675899</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>92001.466114394294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1447,8 +1359,23 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D4" s="1">
+        <v>748.97853731957196</v>
+      </c>
+      <c r="E4" s="1">
+        <v>35949.191362364101</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1732.37581959659</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>95845.041376111796</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1458,8 +1385,23 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D5" s="1">
+        <v>1078.3247042913699</v>
+      </c>
+      <c r="E5" s="1">
+        <v>41385.655568557602</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2051.42488497255</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>98117.404711791707</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1469,8 +1411,23 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D6" s="1">
+        <v>2558.73855992571</v>
+      </c>
+      <c r="E6" s="1">
+        <v>51594.448092163497</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2638.4901581972799</v>
+      </c>
+      <c r="G6" s="1">
+        <v>87.738182751532193</v>
+      </c>
+      <c r="H6" s="1">
+        <v>97210.410166385205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1480,8 +1437,23 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D7" s="1">
+        <v>3991.41740699092</v>
+      </c>
+      <c r="E7" s="1">
+        <v>60490.861182656197</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3369.5524972613398</v>
+      </c>
+      <c r="G7" s="1">
+        <v>346.44176318324702</v>
+      </c>
+      <c r="H7" s="1">
+        <v>102926.86246957201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1491,8 +1463,23 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D8" s="1">
+        <v>6795.5266068207902</v>
+      </c>
+      <c r="E8" s="1">
+        <v>68821.315490219204</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5038.9446489478796</v>
+      </c>
+      <c r="G8" s="1">
+        <v>415.41063117379298</v>
+      </c>
+      <c r="H8" s="1">
+        <v>106206.729450813</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1502,8 +1489,23 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D9" s="1">
+        <v>9220.5814719521404</v>
+      </c>
+      <c r="E9" s="1">
+        <v>75619.978243938502</v>
+      </c>
+      <c r="F9" s="1">
+        <v>7447.6092126076101</v>
+      </c>
+      <c r="G9" s="1">
+        <v>494.44171836475698</v>
+      </c>
+      <c r="H9" s="1">
+        <v>103239.166063706</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1513,8 +1515,23 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D10" s="1">
+        <v>16306.6233185903</v>
+      </c>
+      <c r="E10" s="1">
+        <v>70603.651477848602</v>
+      </c>
+      <c r="F10" s="1">
+        <v>8939.7834843230594</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1322.1845081261999</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100430.495382101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1524,8 +1541,23 @@
       <c r="C11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D11" s="1">
+        <v>25666.444183610602</v>
+      </c>
+      <c r="E11" s="1">
+        <v>66406.970486713195</v>
+      </c>
+      <c r="F11" s="1">
+        <v>7599.00745516807</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4166.9852968654104</v>
+      </c>
+      <c r="H11" s="1">
+        <v>97810.253968283403</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1535,8 +1567,23 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D12" s="1">
+        <v>31068.190418001301</v>
+      </c>
+      <c r="E12" s="1">
+        <v>50955.3786378765</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3877.4105117599802</v>
+      </c>
+      <c r="G12" s="1">
+        <v>7121.4898909630801</v>
+      </c>
+      <c r="H12" s="1">
+        <v>80994.201656676494</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1546,8 +1593,23 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D13" s="1">
+        <v>28562.254090623501</v>
+      </c>
+      <c r="E13" s="1">
+        <v>36209.117019673598</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1267.62332415935</v>
+      </c>
+      <c r="G13" s="1">
+        <v>9753.0242400838306</v>
+      </c>
+      <c r="H13" s="1">
+        <v>59077.403328476401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1557,8 +1619,23 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D14" s="1">
+        <v>33611.392735452697</v>
+      </c>
+      <c r="E14" s="1">
+        <v>31401.300423482498</v>
+      </c>
+      <c r="F14" s="1">
+        <v>217.89948573456999</v>
+      </c>
+      <c r="G14" s="1">
+        <v>15989.268430030899</v>
+      </c>
+      <c r="H14" s="1">
+        <v>54816.379798116403</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1568,8 +1645,23 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D15" s="1">
+        <v>31783.288336023099</v>
+      </c>
+      <c r="E15" s="1">
+        <v>23661.447827027299</v>
+      </c>
+      <c r="F15" s="1">
+        <v>102.968938857062</v>
+      </c>
+      <c r="G15" s="1">
+        <v>18356.632086485599</v>
+      </c>
+      <c r="H15" s="1">
+        <v>44040.047577108096</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1579,11 +1671,23 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D16" s="1">
+        <v>732.17669793488994</v>
+      </c>
+      <c r="E16" s="1">
+        <v>6903.3856171284597</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1882.3261356478499</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>52459.133047528499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1593,11 +1697,23 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D17" s="1">
+        <v>875.66547185091201</v>
+      </c>
+      <c r="E17" s="1">
+        <v>7572.9497652494201</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2063.3176114873099</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>51487.6114650327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1607,11 +1723,23 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D18" s="1">
+        <v>1522.39056592836</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10728.119445366399</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3182.9730794914199</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>53001.885335280604</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1621,11 +1749,23 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D19" s="1">
+        <v>2386.2039972033499</v>
+      </c>
+      <c r="E19" s="1">
+        <v>13516.419112613899</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4173.4852622846001</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>54004.563539681803</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1635,11 +1775,23 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D20" s="1">
+        <v>4904.3715053904198</v>
+      </c>
+      <c r="E20" s="1">
+        <v>18243.6701981068</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5418.7089590147798</v>
+      </c>
+      <c r="G20" s="1">
+        <v>73.9401451264157</v>
+      </c>
+      <c r="H20" s="1">
+        <v>53494.462588376002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1649,11 +1801,23 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D21" s="1">
+        <v>7890.9428204744399</v>
+      </c>
+      <c r="E21" s="1">
+        <v>24637.452332464902</v>
+      </c>
+      <c r="F21" s="1">
+        <v>6607.8055836112298</v>
+      </c>
+      <c r="G21" s="1">
+        <v>319.383499940842</v>
+      </c>
+      <c r="H21" s="1">
+        <v>55783.629033686098</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1663,11 +1827,23 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D22" s="1">
+        <v>13193.520078261499</v>
+      </c>
+      <c r="E22" s="1">
+        <v>35868.234387963697</v>
+      </c>
+      <c r="F22" s="1">
+        <v>8590.7714098890792</v>
+      </c>
+      <c r="G22" s="1">
+        <v>342.058368473749</v>
+      </c>
+      <c r="H22" s="1">
+        <v>55531.209751856397</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1677,11 +1853,23 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D23" s="1">
+        <v>18606.703142693601</v>
+      </c>
+      <c r="E23" s="1">
+        <v>47811.093394094598</v>
+      </c>
+      <c r="F23" s="1">
+        <v>10066.927515371901</v>
+      </c>
+      <c r="G23" s="1">
+        <v>421.23427726812002</v>
+      </c>
+      <c r="H23" s="1">
+        <v>52404.222916664497</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1691,11 +1879,23 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D24" s="1">
+        <v>29286.974768860899</v>
+      </c>
+      <c r="E24" s="1">
+        <v>60906.428978592798</v>
+      </c>
+      <c r="F24" s="1">
+        <v>9740.8776702336709</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1284.67521796611</v>
+      </c>
+      <c r="H24" s="1">
+        <v>48240.554310301603</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1705,11 +1905,23 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D25" s="1">
+        <v>41010.489145052699</v>
+      </c>
+      <c r="E25" s="1">
+        <v>68773.167936683807</v>
+      </c>
+      <c r="F25" s="1">
+        <v>7234.7744116886597</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3492.81836113283</v>
+      </c>
+      <c r="H25" s="1">
+        <v>45361.153274361197</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1719,11 +1931,23 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D26" s="1">
+        <v>41885.195486218399</v>
+      </c>
+      <c r="E26" s="1">
+        <v>63162.831196373998</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3193.9782544847899</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5395.4809739491102</v>
+      </c>
+      <c r="H26" s="1">
+        <v>36008.780525071503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1733,11 +1957,23 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D27" s="1">
+        <v>30568.730726834699</v>
+      </c>
+      <c r="E27" s="1">
+        <v>43769.993921533402</v>
+      </c>
+      <c r="F27" s="1">
+        <v>919.29958004632294</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6418.6206639030597</v>
+      </c>
+      <c r="H27" s="1">
+        <v>23844.600835253401</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -1747,11 +1983,23 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D28" s="1">
+        <v>29682.2221039221</v>
+      </c>
+      <c r="E28" s="1">
+        <v>33925.402817990798</v>
+      </c>
+      <c r="F28" s="1">
+        <v>105.886084134353</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9188.4349323497008</v>
+      </c>
+      <c r="H28" s="1">
+        <v>18875.3969379519</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -1761,8 +2009,20 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="E29">
-        <v>0</v>
+      <c r="D29" s="1">
+        <v>22499.177480744602</v>
+      </c>
+      <c r="E29" s="1">
+        <v>21763.281474445499</v>
+      </c>
+      <c r="F29" s="1">
+        <v>37.156910532311599</v>
+      </c>
+      <c r="G29" s="1">
+        <v>8750.47364491589</v>
+      </c>
+      <c r="H29" s="1">
+        <v>12144.0385964947</v>
       </c>
     </row>
   </sheetData>
@@ -1772,42 +2032,43 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F9C405-CC78-DE47-80BA-51DD73EFCA1A}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="9" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1817,8 +2078,23 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D2" s="1">
+        <v>642.129110645482</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45101.689759668297</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2523.74999829432</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>138801.978834651</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1828,8 +2104,23 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D3" s="1">
+        <v>835.24767500852295</v>
+      </c>
+      <c r="E3" s="1">
+        <v>64924.075297868498</v>
+      </c>
+      <c r="F3" s="1">
+        <v>3002.3680942698702</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>134334.177423841</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1839,8 +2130,23 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D4" s="1">
+        <v>1167.13932798873</v>
+      </c>
+      <c r="E4" s="1">
+        <v>81735.535434642006</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3660.9913132224701</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>135290.46076181901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1850,8 +2156,23 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D5" s="1">
+        <v>1684.4540816368401</v>
+      </c>
+      <c r="E5" s="1">
+        <v>100870.669712984</v>
+      </c>
+      <c r="F5" s="1">
+        <v>4654.6955970973604</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>138678.74731181099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1861,8 +2182,23 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D6" s="1">
+        <v>3726.8103490562698</v>
+      </c>
+      <c r="E6" s="1">
+        <v>111586.798374929</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5163.1622850513504</v>
+      </c>
+      <c r="G6" s="1">
+        <v>339.387898639561</v>
+      </c>
+      <c r="H6" s="1">
+        <v>136953.78567725999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1872,8 +2208,23 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D7" s="1">
+        <v>6962.4320982106001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>140738.44331002099</v>
+      </c>
+      <c r="F7" s="1">
+        <v>6694.3701977393903</v>
+      </c>
+      <c r="G7" s="1">
+        <v>838.63762340512596</v>
+      </c>
+      <c r="H7" s="1">
+        <v>145904.23741587199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1883,8 +2234,23 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D8" s="1">
+        <v>10496.916387537</v>
+      </c>
+      <c r="E8" s="1">
+        <v>144889.84020291499</v>
+      </c>
+      <c r="F8" s="1">
+        <v>9029.3727817545896</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1030.3448775004799</v>
+      </c>
+      <c r="H8" s="1">
+        <v>146698.36388370799</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1894,8 +2260,23 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D9" s="1">
+        <v>17270.020826055301</v>
+      </c>
+      <c r="E9" s="1">
+        <v>144759.89546308201</v>
+      </c>
+      <c r="F9" s="1">
+        <v>12517.466134808101</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1405.4112792992701</v>
+      </c>
+      <c r="H9" s="1">
+        <v>139865.58457303501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1905,8 +2286,23 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D10" s="1">
+        <v>26222.9007885106</v>
+      </c>
+      <c r="E10" s="1">
+        <v>137165.71236874399</v>
+      </c>
+      <c r="F10" s="1">
+        <v>12913.7106924167</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3133.34653567033</v>
+      </c>
+      <c r="H10" s="1">
+        <v>138761.047798849</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1916,8 +2312,23 @@
       <c r="C11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D11" s="1">
+        <v>42073.098996386798</v>
+      </c>
+      <c r="E11" s="1">
+        <v>128392.78024285</v>
+      </c>
+      <c r="F11" s="1">
+        <v>11900.0316725886</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7203.4588355820897</v>
+      </c>
+      <c r="H11" s="1">
+        <v>142257.93824029199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1927,8 +2338,23 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D12" s="1">
+        <v>45614.958709516002</v>
+      </c>
+      <c r="E12" s="1">
+        <v>100310.28210771301</v>
+      </c>
+      <c r="F12" s="1">
+        <v>7616.1550117172501</v>
+      </c>
+      <c r="G12" s="1">
+        <v>12288.5092118624</v>
+      </c>
+      <c r="H12" s="1">
+        <v>118913.54042939701</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1938,8 +2364,23 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D13" s="1">
+        <v>44305.570506391399</v>
+      </c>
+      <c r="E13" s="1">
+        <v>57311.304626032499</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2187.2252600194101</v>
+      </c>
+      <c r="G13" s="1">
+        <v>17006.707577093199</v>
+      </c>
+      <c r="H13" s="1">
+        <v>84294.887451215094</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1949,8 +2390,23 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D14" s="1">
+        <v>49483.565136865298</v>
+      </c>
+      <c r="E14" s="1">
+        <v>49737.344193223798</v>
+      </c>
+      <c r="F14" s="1">
+        <v>589.961836999159</v>
+      </c>
+      <c r="G14" s="1">
+        <v>26251.522138160799</v>
+      </c>
+      <c r="H14" s="1">
+        <v>78378.019836771899</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1960,8 +2416,23 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D15" s="1">
+        <v>50726.232449147203</v>
+      </c>
+      <c r="E15" s="1">
+        <v>35934.197858170097</v>
+      </c>
+      <c r="F15" s="1">
+        <v>252.87416136956799</v>
+      </c>
+      <c r="G15" s="1">
+        <v>29294.222935033202</v>
+      </c>
+      <c r="H15" s="1">
+        <v>60698.698858546697</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1971,11 +2442,23 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D16" s="1">
+        <v>1347.3945715340301</v>
+      </c>
+      <c r="E16" s="1">
+        <v>15262.467575066201</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3799.4856851865602</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>79932.820095374904</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1985,11 +2468,23 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D17" s="1">
+        <v>1649.9146067435099</v>
+      </c>
+      <c r="E17" s="1">
+        <v>17262.374967923501</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4799.7685902288704</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>75294.311268587902</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1999,11 +2494,23 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D18" s="1">
+        <v>2371.2075734478499</v>
+      </c>
+      <c r="E18" s="1">
+        <v>22088.826810386101</v>
+      </c>
+      <c r="F18" s="1">
+        <v>6413.2160890507603</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>74562.117488012795</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2013,11 +2520,23 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D19" s="1">
+        <v>3615.3864966910901</v>
+      </c>
+      <c r="E19" s="1">
+        <v>28666.023924118301</v>
+      </c>
+      <c r="F19" s="1">
+        <v>8418.2629535505694</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>77561.278356379102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2027,11 +2546,23 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D20" s="1">
+        <v>6517.7431013639898</v>
+      </c>
+      <c r="E20" s="1">
+        <v>33451.674914397699</v>
+      </c>
+      <c r="F20" s="1">
+        <v>9649.9671734145595</v>
+      </c>
+      <c r="G20" s="1">
+        <v>304.33648533112603</v>
+      </c>
+      <c r="H20" s="1">
+        <v>75885.270495522505</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -2041,11 +2572,23 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D21" s="1">
+        <v>11825.4136507613</v>
+      </c>
+      <c r="E21" s="1">
+        <v>50711.385527780702</v>
+      </c>
+      <c r="F21" s="1">
+        <v>12117.2445017883</v>
+      </c>
+      <c r="G21" s="1">
+        <v>730.47820433884601</v>
+      </c>
+      <c r="H21" s="1">
+        <v>79983.308623345103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2055,11 +2598,23 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D22" s="1">
+        <v>18114.1294362927</v>
+      </c>
+      <c r="E22" s="1">
+        <v>62394.887720340397</v>
+      </c>
+      <c r="F22" s="1">
+        <v>13849.6866874922</v>
+      </c>
+      <c r="G22" s="1">
+        <v>886.98284525974498</v>
+      </c>
+      <c r="H22" s="1">
+        <v>77694.023051982906</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2069,11 +2624,23 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D23" s="1">
+        <v>28165.924911537699</v>
+      </c>
+      <c r="E23" s="1">
+        <v>79332.442986173002</v>
+      </c>
+      <c r="F23" s="1">
+        <v>17086.024151701298</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1245.8545953625801</v>
+      </c>
+      <c r="H23" s="1">
+        <v>71221.094453531696</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2083,11 +2650,23 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D24" s="1">
+        <v>39976.591433394096</v>
+      </c>
+      <c r="E24" s="1">
+        <v>93784.351040393201</v>
+      </c>
+      <c r="F24" s="1">
+        <v>15428.0057651596</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2838.05794219465</v>
+      </c>
+      <c r="H24" s="1">
+        <v>67354.644457613598</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -2097,11 +2676,23 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D25" s="1">
+        <v>59567.671669830503</v>
+      </c>
+      <c r="E25" s="1">
+        <v>112349.387242595</v>
+      </c>
+      <c r="F25" s="1">
+        <v>12945.5492635112</v>
+      </c>
+      <c r="G25" s="1">
+        <v>6364.5755757529396</v>
+      </c>
+      <c r="H25" s="1">
+        <v>67257.735444433099</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2111,11 +2702,23 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D26" s="1">
+        <v>56711.031005466997</v>
+      </c>
+      <c r="E26" s="1">
+        <v>98582.7432954994</v>
+      </c>
+      <c r="F26" s="1">
+        <v>7729.5594035261802</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9780.1680736949093</v>
+      </c>
+      <c r="H26" s="1">
+        <v>53498.621752128704</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -2125,11 +2728,23 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D27" s="1">
+        <v>44998.082220413002</v>
+      </c>
+      <c r="E27" s="1">
+        <v>62034.502835804902</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1873.36497002801</v>
+      </c>
+      <c r="G27" s="1">
+        <v>11852.898192500599</v>
+      </c>
+      <c r="H27" s="1">
+        <v>34551.895088555597</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -2139,11 +2754,23 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D28" s="1">
+        <v>40759.000567518902</v>
+      </c>
+      <c r="E28" s="1">
+        <v>47209.029960939399</v>
+      </c>
+      <c r="F28" s="1">
+        <v>307.24312553894498</v>
+      </c>
+      <c r="G28" s="1">
+        <v>16327.443986461099</v>
+      </c>
+      <c r="H28" s="1">
+        <v>27665.411221903702</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -2153,8 +2780,20 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="E29">
-        <v>0</v>
+      <c r="D29" s="1">
+        <v>32994.459846837803</v>
+      </c>
+      <c r="E29" s="1">
+        <v>29950.4557205399</v>
+      </c>
+      <c r="F29" s="1">
+        <v>101.43299458342101</v>
+      </c>
+      <c r="G29" s="1">
+        <v>15031.7875034074</v>
+      </c>
+      <c r="H29" s="1">
+        <v>16842.1456445771</v>
       </c>
     </row>
   </sheetData>

--- a/data/GBD_diseases.xlsx
+++ b/data/GBD_diseases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83D7863-C27C-1F48-9F3D-805C6D2B18A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C32562-DB37-AE4F-8B89-7DAF5755FF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31500" yWindow="-1380" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
+    <workbookView xWindow="34240" yWindow="-1160" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="25">
   <si>
     <t>Male</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>age_grp</t>
+  </si>
+  <si>
+    <t>dep_prevalence</t>
   </si>
 </sst>
 </file>
@@ -490,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD0F75B-B6CB-6D48-ABCA-C0DE307A97B8}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -498,9 +501,10 @@
     <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -525,8 +529,11 @@
       <c r="H1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -551,8 +558,11 @@
       <c r="H2" s="1">
         <v>110106.980466972</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1">
+        <v>67784.402232364999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -577,8 +587,11 @@
       <c r="H3" s="1">
         <v>109941.189467854</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="1">
+        <v>68455.523531892293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -603,8 +616,11 @@
       <c r="H4" s="1">
         <v>115456.646754588</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="1">
+        <v>71858.1892132434</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -629,8 +645,11 @@
       <c r="H5" s="1">
         <v>117815.618668783</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" s="1">
+        <v>74423.611475318394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -655,8 +674,11 @@
       <c r="H6" s="1">
         <v>117181.94292290301</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" s="1">
+        <v>74861.602089678301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -681,8 +703,11 @@
       <c r="H7" s="1">
         <v>124337.67221672799</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" s="1">
+        <v>81381.066947812506</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -707,8 +732,11 @@
       <c r="H8" s="1">
         <v>124548.53842968799</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" s="1">
+        <v>83143.184970693299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -733,8 +761,11 @@
       <c r="H9" s="1">
         <v>121389.983337382</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" s="1">
+        <v>82016.682079551902</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -759,8 +790,11 @@
       <c r="H10" s="1">
         <v>117939.92514770701</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" s="1">
+        <v>80054.931037718095</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -785,8 +819,11 @@
       <c r="H11" s="1">
         <v>117025.30046122101</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" s="1">
+        <v>80192.433778004197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -811,8 +848,11 @@
       <c r="H12" s="1">
         <v>96232.371325058106</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" s="1">
+        <v>66571.8857277934</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -837,8 +877,11 @@
       <c r="H13" s="1">
         <v>71576.162778811806</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" s="1">
+        <v>50329.169102781801</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -863,8 +906,11 @@
       <c r="H14" s="1">
         <v>65942.646528924204</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14" s="1">
+        <v>47623.047709947503</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -889,8 +935,11 @@
       <c r="H15" s="1">
         <v>51323.210853908997</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" s="1">
+        <v>37414.906158514903</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -915,8 +964,11 @@
       <c r="H16" s="1">
         <v>63725.650599513603</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" s="1">
+        <v>40009.3949797065</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -941,8 +993,11 @@
       <c r="H17" s="1">
         <v>61953.617402941702</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" s="1">
+        <v>39267.500493782201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -967,8 +1022,11 @@
       <c r="H18" s="1">
         <v>63951.726487806802</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" s="1">
+        <v>40734.897141880298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -993,8 +1051,11 @@
       <c r="H19" s="1">
         <v>65499.398155419098</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" s="1">
+        <v>42042.584455301498</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1019,8 +1080,11 @@
       <c r="H20" s="1">
         <v>65091.9510618442</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" s="1">
+        <v>42178.021680422098</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1109,11 @@
       <c r="H21" s="1">
         <v>67565.817499864803</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" s="1">
+        <v>44342.9579671881</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1071,8 +1138,11 @@
       <c r="H22" s="1">
         <v>65314.3905427461</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" s="1">
+        <v>43119.024335203401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1097,8 +1167,11 @@
       <c r="H23" s="1">
         <v>61507.848943434699</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23" s="1">
+        <v>40989.765822723901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1123,8 +1196,11 @@
       <c r="H24" s="1">
         <v>57097.117568491303</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" s="1">
+        <v>38169.336360151698</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1149,8 +1225,11 @@
       <c r="H25" s="1">
         <v>54760.295815320802</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" s="1">
+        <v>36847.669776009199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1175,8 +1254,11 @@
       <c r="H26" s="1">
         <v>43206.315763751198</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26" s="1">
+        <v>29203.54883887</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1201,8 +1283,11 @@
       <c r="H27" s="1">
         <v>29283.088765753499</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27" s="1">
+        <v>20022.905824427799</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -1227,8 +1312,11 @@
       <c r="H28" s="1">
         <v>22967.3339007953</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28" s="1">
+        <v>16020.604332495999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -1252,6 +1340,9 @@
       </c>
       <c r="H29" s="1">
         <v>14170.4127573039</v>
+      </c>
+      <c r="I29" s="1">
+        <v>9943.3943236052</v>
       </c>
     </row>
   </sheetData>
@@ -1261,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E002562B-DD6F-164B-BC33-738F7B5F11A1}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -1269,9 +1360,10 @@
     <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1296,8 +1388,11 @@
       <c r="H1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1322,8 +1417,11 @@
       <c r="H2" s="1">
         <v>90350.229755512599</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1">
+        <v>55198.5750668447</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1348,8 +1446,11 @@
       <c r="H3" s="1">
         <v>92001.466114394294</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="1">
+        <v>56309.240982367999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1374,8 +1475,11 @@
       <c r="H4" s="1">
         <v>95845.041376111796</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="1">
+        <v>57536.610010473501</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1400,8 +1504,11 @@
       <c r="H5" s="1">
         <v>98117.404711791707</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" s="1">
+        <v>62314.640167808597</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1426,8 +1533,11 @@
       <c r="H6" s="1">
         <v>97210.410166385205</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" s="1">
+        <v>62045.2456145748</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1452,8 +1562,11 @@
       <c r="H7" s="1">
         <v>102926.86246957201</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" s="1">
+        <v>69846.065165256805</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1478,8 +1591,11 @@
       <c r="H8" s="1">
         <v>106206.729450813</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" s="1">
+        <v>70709.505373722495</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1504,8 +1620,11 @@
       <c r="H9" s="1">
         <v>103239.166063706</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" s="1">
+        <v>71121.424648442699</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1530,8 +1649,11 @@
       <c r="H10" s="1">
         <v>100430.495382101</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" s="1">
+        <v>69780.673663897003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1556,8 +1678,11 @@
       <c r="H11" s="1">
         <v>97810.253968283403</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" s="1">
+        <v>70084.460442772601</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1582,8 +1707,11 @@
       <c r="H12" s="1">
         <v>80994.201656676494</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" s="1">
+        <v>57142.800067876698</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1608,8 +1736,11 @@
       <c r="H13" s="1">
         <v>59077.403328476401</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" s="1">
+        <v>43155.481129965301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1634,8 +1765,11 @@
       <c r="H14" s="1">
         <v>54816.379798116403</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14" s="1">
+        <v>40189.834988506198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1660,8 +1794,11 @@
       <c r="H15" s="1">
         <v>44040.047577108096</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" s="1">
+        <v>30742.587748637801</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1686,8 +1823,11 @@
       <c r="H16" s="1">
         <v>52459.133047528499</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" s="1">
+        <v>32341.602525145499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1712,8 +1852,11 @@
       <c r="H17" s="1">
         <v>51487.6114650327</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" s="1">
+        <v>31226.703848296798</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1738,8 +1881,11 @@
       <c r="H18" s="1">
         <v>53001.885335280604</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" s="1">
+        <v>31788.756570498401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1764,8 +1910,11 @@
       <c r="H19" s="1">
         <v>54004.563539681803</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" s="1">
+        <v>34295.186404271903</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1790,8 +1939,11 @@
       <c r="H20" s="1">
         <v>53494.462588376002</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" s="1">
+        <v>33905.283822597601</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1816,8 +1968,11 @@
       <c r="H21" s="1">
         <v>55783.629033686098</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" s="1">
+        <v>37632.573317415503</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1842,8 +1997,11 @@
       <c r="H22" s="1">
         <v>55531.209751856397</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" s="1">
+        <v>35983.486274115203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1868,8 +2026,11 @@
       <c r="H23" s="1">
         <v>52404.222916664497</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23" s="1">
+        <v>34801.993057920001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1894,8 +2055,11 @@
       <c r="H24" s="1">
         <v>48240.554310301603</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" s="1">
+        <v>32727.3315273232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1920,8 +2084,11 @@
       <c r="H25" s="1">
         <v>45361.153274361197</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" s="1">
+        <v>31382.510572155101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1946,8 +2113,11 @@
       <c r="H26" s="1">
         <v>36008.780525071503</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26" s="1">
+        <v>24306.229015712201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1972,8 +2142,11 @@
       <c r="H27" s="1">
         <v>23844.600835253401</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27" s="1">
+        <v>16784.8676980251</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -1998,8 +2171,11 @@
       <c r="H28" s="1">
         <v>18875.3969379519</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28" s="1">
+        <v>13090.894410745501</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -2023,6 +2199,9 @@
       </c>
       <c r="H29" s="1">
         <v>12144.0385964947</v>
+      </c>
+      <c r="I29" s="1">
+        <v>7989.5474402997597</v>
       </c>
     </row>
   </sheetData>
@@ -2032,7 +2211,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F9C405-CC78-DE47-80BA-51DD73EFCA1A}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -2040,9 +2219,10 @@
     <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -2067,8 +2247,11 @@
       <c r="H1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2093,8 +2276,11 @@
       <c r="H2" s="1">
         <v>138801.978834651</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1">
+        <v>79621.9456363192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2119,8 +2305,11 @@
       <c r="H3" s="1">
         <v>134334.177423841</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="1">
+        <v>80433.486807937195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2145,8 +2334,11 @@
       <c r="H4" s="1">
         <v>135290.46076181901</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="1">
+        <v>84230.089263609596</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2171,8 +2363,11 @@
       <c r="H5" s="1">
         <v>138678.74731181099</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" s="1">
+        <v>86067.449018426298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2197,8 +2392,11 @@
       <c r="H6" s="1">
         <v>136953.78567725999</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" s="1">
+        <v>89640.730596265406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2223,8 +2421,11 @@
       <c r="H7" s="1">
         <v>145904.23741587199</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" s="1">
+        <v>93555.262635121806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2249,8 +2450,11 @@
       <c r="H8" s="1">
         <v>146698.36388370799</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" s="1">
+        <v>98613.814029934598</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2275,8 +2479,11 @@
       <c r="H9" s="1">
         <v>139865.58457303501</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" s="1">
+        <v>97260.106005538793</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -2301,8 +2508,11 @@
       <c r="H10" s="1">
         <v>138761.047798849</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" s="1">
+        <v>95299.347541525305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2327,8 +2537,11 @@
       <c r="H11" s="1">
         <v>142257.93824029199</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" s="1">
+        <v>92332.258729937996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -2353,8 +2566,11 @@
       <c r="H12" s="1">
         <v>118913.54042939701</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" s="1">
+        <v>79845.600196532905</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2379,8 +2595,11 @@
       <c r="H13" s="1">
         <v>84294.887451215094</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" s="1">
+        <v>58632.261798236999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -2405,8 +2624,11 @@
       <c r="H14" s="1">
         <v>78378.019836771899</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14" s="1">
+        <v>55905.972149341003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -2431,8 +2653,11 @@
       <c r="H15" s="1">
         <v>60698.698858546697</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" s="1">
+        <v>46098.252192666499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2457,8 +2682,11 @@
       <c r="H16" s="1">
         <v>79932.820095374904</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" s="1">
+        <v>47283.987962690298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2483,8 +2711,11 @@
       <c r="H17" s="1">
         <v>75294.311268587902</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" s="1">
+        <v>47088.315859173301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -2509,8 +2740,11 @@
       <c r="H18" s="1">
         <v>74562.117488012795</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" s="1">
+        <v>48856.6953063236</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2535,8 +2769,11 @@
       <c r="H19" s="1">
         <v>77561.278356379102</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" s="1">
+        <v>49788.700798170998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2561,8 +2798,11 @@
       <c r="H20" s="1">
         <v>75885.270495522505</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" s="1">
+        <v>51466.440542918303</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -2587,8 +2827,11 @@
       <c r="H21" s="1">
         <v>79983.308623345103</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" s="1">
+        <v>53178.667848150399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2613,8 +2856,11 @@
       <c r="H22" s="1">
         <v>77694.023051982906</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" s="1">
+        <v>52582.551384206199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2639,8 +2885,11 @@
       <c r="H23" s="1">
         <v>71221.094453531696</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23" s="1">
+        <v>50016.900051043202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2665,8 +2914,11 @@
       <c r="H24" s="1">
         <v>67354.644457613598</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" s="1">
+        <v>45813.211646001699</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -2691,8 +2943,11 @@
       <c r="H25" s="1">
         <v>67257.735444433099</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" s="1">
+        <v>43471.406191182097</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2717,8 +2972,11 @@
       <c r="H26" s="1">
         <v>53498.621752128704</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26" s="1">
+        <v>36043.679827715503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -2743,8 +3001,11 @@
       <c r="H27" s="1">
         <v>34551.895088555597</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27" s="1">
+        <v>23867.2419793607</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -2769,8 +3030,11 @@
       <c r="H28" s="1">
         <v>27665.411221903702</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28" s="1">
+        <v>19303.870779180601</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -2794,6 +3058,9 @@
       </c>
       <c r="H29" s="1">
         <v>16842.1456445771</v>
+      </c>
+      <c r="I29" s="1">
+        <v>12626.1323890277</v>
       </c>
     </row>
   </sheetData>

--- a/data/GBD_diseases.xlsx
+++ b/data/GBD_diseases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C32562-DB37-AE4F-8B89-7DAF5755FF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4D7074-3993-FF4A-8B8E-CE2570A8A7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34240" yWindow="-1160" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="16100" activeTab="2" xr2:uid="{E681AD37-9457-C84A-B54A-A4A5BA37FC49}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="27">
   <si>
     <t>Male</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>dep_prevalence</t>
+  </si>
+  <si>
+    <t>bc_incidence</t>
+  </si>
+  <si>
+    <t>cc_incidence</t>
   </si>
 </sst>
 </file>
@@ -493,18 +499,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD0F75B-B6CB-6D48-ABCA-C0DE307A97B8}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -515,25 +523,31 @@
         <v>21</v>
       </c>
       <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -543,26 +557,32 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
+        <v>46.985244064993502</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30.180880144163499</v>
+      </c>
+      <c r="F2" s="2">
         <v>470.69469038044798</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>31895.028700513602</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1">
         <v>1820.60209060134</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
         <v>110106.980466972</v>
       </c>
-      <c r="I2" s="1">
+      <c r="K2" s="1">
         <v>67784.402232364999</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -572,26 +592,32 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
+        <v>262.93937582697203</v>
+      </c>
+      <c r="E3" s="1">
+        <v>51.168487926524399</v>
+      </c>
+      <c r="F3" s="2">
         <v>632.77539815350804</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>41373.529924294002</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H3" s="1">
         <v>2169.7299767801601</v>
       </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
         <v>109941.189467854</v>
       </c>
-      <c r="I3" s="1">
+      <c r="K3" s="1">
         <v>68455.523531892293</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -601,26 +627,32 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
+        <v>910.86506240088602</v>
+      </c>
+      <c r="E4" s="1">
+        <v>118.93048707633901</v>
+      </c>
+      <c r="F4" s="2">
         <v>940.43433537620399</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>54827.829429694502</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1">
         <v>2650.1162851320801</v>
       </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
         <v>115456.646754588</v>
       </c>
-      <c r="I4" s="1">
+      <c r="K4" s="1">
         <v>71858.1892132434</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -630,26 +662,32 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
+        <v>1869.5575392528101</v>
+      </c>
+      <c r="E5" s="1">
+        <v>221.81545648879501</v>
+      </c>
+      <c r="F5" s="2">
         <v>1349.06519303611</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>67646.912270110799</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>3193.72590896884</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
         <v>117815.618668783</v>
       </c>
-      <c r="I5" s="1">
+      <c r="K5" s="1">
         <v>74423.611475318394</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -659,26 +697,32 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
+        <v>3605.9935562933301</v>
+      </c>
+      <c r="E6" s="1">
+        <v>386.46161229705501</v>
+      </c>
+      <c r="F6" s="2">
         <v>3101.65917634979</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>78426.804447342205</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>3757.3592830689499</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>200.45055222268201</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>117181.94292290301</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>74861.602089678301</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -688,26 +732,32 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
+        <v>5662.1815927131001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>797.95970821040396</v>
+      </c>
+      <c r="F7" s="2">
         <v>5221.7732342678501</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>94599.433891750406</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>4734.0420195553697</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>579.92204176205803</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>124337.67221672799</v>
       </c>
-      <c r="I7" s="1">
+      <c r="K7" s="1">
         <v>81381.066947812506</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -717,26 +767,32 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
+        <v>6467.0407539628004</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1231.72119404051</v>
+      </c>
+      <c r="F8" s="2">
         <v>8374.8103610041799</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>101403.734074696</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>6858.1379876118799</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>713.40720180574601</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>124548.53842968799</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>83143.184970693299</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -746,26 +802,32 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
+        <v>6677.6200249973599</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1727.60048485835</v>
+      </c>
+      <c r="F9" s="2">
         <v>12430.148542774999</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>105611.803169869</v>
       </c>
-      <c r="F9" s="1">
+      <c r="H9" s="1">
         <v>10022.503228932601</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>898.23776155674796</v>
       </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
         <v>121389.983337382</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>82016.682079551902</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -775,26 +837,32 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
+        <v>7493.3171621217898</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2362.3650670424399</v>
+      </c>
+      <c r="F10" s="2">
         <v>20587.442224745701</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>101256.038155812</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>10803.393482634399</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>2072.6209123938602</v>
       </c>
-      <c r="H10" s="1">
+      <c r="J10" s="1">
         <v>117939.92514770701</v>
       </c>
-      <c r="I10" s="1">
+      <c r="K10" s="1">
         <v>80054.931037718095</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -804,26 +872,32 @@
       <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
+        <v>8129.2998451592402</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3065.8244649973399</v>
+      </c>
+      <c r="F11" s="2">
         <v>32657.341173983099</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
         <v>91242.370890545499</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="1">
         <v>9873.4820198206107</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>5605.3712666789497</v>
       </c>
-      <c r="H11" s="1">
+      <c r="J11" s="1">
         <v>117025.30046122101</v>
       </c>
-      <c r="I11" s="1">
+      <c r="K11" s="1">
         <v>80192.433778004197</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -833,26 +907,32 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
+        <v>7197.55395485193</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3517.6104937896998</v>
+      </c>
+      <c r="F12" s="2">
         <v>37338.508895075996</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>70323.291408803503</v>
       </c>
-      <c r="F12" s="1">
+      <c r="H12" s="1">
         <v>5928.3316071394702</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>9543.1648218351602</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>96232.371325058106</v>
       </c>
-      <c r="I12" s="1">
+      <c r="K12" s="1">
         <v>66571.8857277934</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -862,26 +942,32 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
+        <v>4805.9454763048898</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3110.6583228335198</v>
+      </c>
+      <c r="F13" s="2">
         <v>35467.572533225699</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>45409.990592704802</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>1758.9273243308801</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>12999.2391768621</v>
       </c>
-      <c r="H13" s="1">
+      <c r="J13" s="1">
         <v>71576.162778811806</v>
       </c>
-      <c r="I13" s="1">
+      <c r="K13" s="1">
         <v>50329.169102781801</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -891,26 +977,32 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
+        <v>4703.9879333736098</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3839.8657174885202</v>
+      </c>
+      <c r="F14" s="2">
         <v>40843.165995684503</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>40071.020130189499</v>
       </c>
-      <c r="F14" s="1">
+      <c r="H14" s="1">
         <v>380.459165983319</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>20835.983559038701</v>
       </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
         <v>65942.646528924204</v>
       </c>
-      <c r="I14" s="1">
+      <c r="K14" s="1">
         <v>47623.047709947503</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -920,26 +1012,32 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
+        <v>3964.1039772608001</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3741.5928706325499</v>
+      </c>
+      <c r="F15" s="2">
         <v>39393.748689389802</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>30087.313673168901</v>
       </c>
-      <c r="F15" s="1">
+      <c r="H15" s="1">
         <v>167.01273980801099</v>
       </c>
-      <c r="G15" s="1">
+      <c r="I15" s="1">
         <v>23167.833796081701</v>
       </c>
-      <c r="H15" s="1">
+      <c r="J15" s="1">
         <v>51323.210853908997</v>
       </c>
-      <c r="I15" s="1">
+      <c r="K15" s="1">
         <v>37414.906158514903</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -949,26 +1047,29 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="1">
+        <v>35.868559274026403</v>
+      </c>
+      <c r="F16" s="2">
         <v>979.590678637667</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>10547.1055404502</v>
       </c>
-      <c r="F16" s="1">
+      <c r="H16" s="1">
         <v>2773.2923883325602</v>
       </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
         <v>63725.650599513603</v>
       </c>
-      <c r="I16" s="1">
+      <c r="K16" s="1">
         <v>40009.3949797065</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -978,26 +1079,29 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="1">
+        <v>61.204729369523598</v>
+      </c>
+      <c r="F17" s="2">
         <v>1201.93972038215</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>11796.8720129139</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>3374.0731419662402</v>
       </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
         <v>61953.617402941702</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>39267.500493782201</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1007,26 +1111,29 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="1">
+        <v>166.91730541291901</v>
+      </c>
+      <c r="F18" s="2">
         <v>1854.4928007996</v>
       </c>
-      <c r="E18" s="1">
+      <c r="G18" s="1">
         <v>15570.378567695199</v>
       </c>
-      <c r="F18" s="1">
+      <c r="H18" s="1">
         <v>4659.5681303445999</v>
       </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <v>63951.726487806802</v>
       </c>
-      <c r="I18" s="1">
+      <c r="K18" s="1">
         <v>40734.897141880298</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1036,26 +1143,29 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="1">
+        <v>259.46955109795101</v>
+      </c>
+      <c r="F19" s="2">
         <v>2911.6926748257501</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>19831.435365161298</v>
       </c>
-      <c r="F19" s="1">
+      <c r="H19" s="1">
         <v>6242.1614464206496</v>
       </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
         <v>65499.398155419098</v>
       </c>
-      <c r="I19" s="1">
+      <c r="K19" s="1">
         <v>42042.584455301498</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1065,26 +1175,29 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="1">
+        <v>393.18848480685102</v>
+      </c>
+      <c r="F20" s="2">
         <v>5659.6219309011904</v>
       </c>
-      <c r="E20" s="1">
+      <c r="G20" s="1">
         <v>25267.382254248801</v>
       </c>
-      <c r="F20" s="1">
+      <c r="H20" s="1">
         <v>7473.8461896226499</v>
       </c>
-      <c r="G20" s="1">
+      <c r="I20" s="1">
         <v>179.37030847911001</v>
       </c>
-      <c r="H20" s="1">
+      <c r="J20" s="1">
         <v>65091.9510618442</v>
       </c>
-      <c r="I20" s="1">
+      <c r="K20" s="1">
         <v>42178.021680422098</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1094,26 +1207,29 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="1">
+        <v>847.04448251226904</v>
+      </c>
+      <c r="F21" s="2">
         <v>9575.0456011774895</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>36274.301361196303</v>
       </c>
-      <c r="F21" s="1">
+      <c r="H21" s="1">
         <v>8962.2641997762894</v>
       </c>
-      <c r="G21" s="1">
+      <c r="I21" s="1">
         <v>512.98459175131802</v>
       </c>
-      <c r="H21" s="1">
+      <c r="J21" s="1">
         <v>67565.817499864803</v>
       </c>
-      <c r="I21" s="1">
+      <c r="K21" s="1">
         <v>44342.9579671881</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1123,26 +1239,29 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="1">
+        <v>1555.83509237306</v>
+      </c>
+      <c r="F22" s="2">
         <v>15463.018047597399</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>47480.353174948003</v>
       </c>
-      <c r="F22" s="1">
+      <c r="H22" s="1">
         <v>10952.9360535551</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>608.76121231193997</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
         <v>65314.3905427461</v>
       </c>
-      <c r="I22" s="1">
+      <c r="K22" s="1">
         <v>43119.024335203401</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1152,26 +1271,29 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="2">
+      <c r="E23" s="1">
+        <v>2352.3323735684398</v>
+      </c>
+      <c r="F23" s="2">
         <v>22944.7611337993</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>62358.169072636701</v>
       </c>
-      <c r="F23" s="1">
+      <c r="H23" s="1">
         <v>13488.6125537559</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>799.52407369711796</v>
       </c>
-      <c r="H23" s="1">
+      <c r="J23" s="1">
         <v>61507.848943434699</v>
       </c>
-      <c r="I23" s="1">
+      <c r="K23" s="1">
         <v>40989.765822723901</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1181,26 +1303,29 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="1">
+        <v>3607.7303284606501</v>
+      </c>
+      <c r="F24" s="2">
         <v>34012.705162054197</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>76354.694622921394</v>
       </c>
-      <c r="F24" s="1">
+      <c r="H24" s="1">
         <v>12523.905111943001</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>1937.18755936714</v>
       </c>
-      <c r="H24" s="1">
+      <c r="J24" s="1">
         <v>57097.117568491303</v>
       </c>
-      <c r="I24" s="1">
+      <c r="K24" s="1">
         <v>38169.336360151698</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1210,26 +1335,29 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="2">
+      <c r="E25" s="1">
+        <v>4958.17627766639</v>
+      </c>
+      <c r="F25" s="2">
         <v>49162.048989562601</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>86867.783459435304</v>
       </c>
-      <c r="F25" s="1">
+      <c r="H25" s="1">
         <v>9641.3463135489092</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>4766.2133119480304</v>
       </c>
-      <c r="H25" s="1">
+      <c r="J25" s="1">
         <v>54760.295815320802</v>
       </c>
-      <c r="I25" s="1">
+      <c r="K25" s="1">
         <v>36847.669776009199</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1239,26 +1367,29 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="2">
+      <c r="E26" s="1">
+        <v>5556.5951131483698</v>
+      </c>
+      <c r="F26" s="2">
         <v>48399.188138501297</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>78052.987440609199</v>
       </c>
-      <c r="F26" s="1">
+      <c r="H26" s="1">
         <v>5121.7042037784004</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>7503.2825109897203</v>
       </c>
-      <c r="H26" s="1">
+      <c r="J26" s="1">
         <v>43206.315763751198</v>
       </c>
-      <c r="I26" s="1">
+      <c r="K26" s="1">
         <v>29203.54883887</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1268,26 +1399,29 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="2">
+      <c r="E27" s="1">
+        <v>4029.8665304145402</v>
+      </c>
+      <c r="F27" s="2">
         <v>36791.664427351898</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>51419.864913194702</v>
       </c>
-      <c r="F27" s="1">
+      <c r="H27" s="1">
         <v>1331.2874336208299</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>8917.9373916232998</v>
       </c>
-      <c r="H27" s="1">
+      <c r="J27" s="1">
         <v>29283.088765753499</v>
       </c>
-      <c r="I27" s="1">
+      <c r="K27" s="1">
         <v>20022.905824427799</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -1297,26 +1431,29 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="2">
+      <c r="E28" s="1">
+        <v>3818.6111722422902</v>
+      </c>
+      <c r="F28" s="2">
         <v>34848.668941745302</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>40352.991684315602</v>
       </c>
-      <c r="F28" s="1">
+      <c r="H28" s="1">
         <v>193.27290625277899</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>12279.956847609799</v>
       </c>
-      <c r="H28" s="1">
+      <c r="J28" s="1">
         <v>22967.3339007953</v>
       </c>
-      <c r="I28" s="1">
+      <c r="K28" s="1">
         <v>16020.604332495999</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -1326,22 +1463,25 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="2">
+      <c r="E29" s="1">
+        <v>3123.0127465436599</v>
+      </c>
+      <c r="F29" s="2">
         <v>27231.105850723201</v>
       </c>
-      <c r="E29" s="1">
+      <c r="G29" s="1">
         <v>25958.0931464733</v>
       </c>
-      <c r="F29" s="1">
+      <c r="H29" s="1">
         <v>67.897980072262897</v>
       </c>
-      <c r="G29" s="1">
+      <c r="I29" s="1">
         <v>11516.040906820101</v>
       </c>
-      <c r="H29" s="1">
+      <c r="J29" s="1">
         <v>14170.4127573039</v>
       </c>
-      <c r="I29" s="1">
+      <c r="K29" s="1">
         <v>9943.3943236052</v>
       </c>
     </row>
@@ -1352,18 +1492,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E002562B-DD6F-164B-BC33-738F7B5F11A1}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1374,25 +1516,31 @@
         <v>21</v>
       </c>
       <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1403,25 +1551,31 @@
         <v>15</v>
       </c>
       <c r="D2" s="1">
+        <v>36.159928838606099</v>
+      </c>
+      <c r="E2" s="1">
+        <v>22.034416734194401</v>
+      </c>
+      <c r="F2" s="1">
         <v>355.32041082233798</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>20535.585789194702</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1">
         <v>1205.6450211404399</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
         <v>90350.229755512599</v>
       </c>
-      <c r="I2" s="1">
+      <c r="K2" s="1">
         <v>55198.5750668447</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1432,25 +1586,31 @@
         <v>15</v>
       </c>
       <c r="D3" s="1">
+        <v>210.334715759067</v>
+      </c>
+      <c r="E3" s="1">
+        <v>39.4145865474269</v>
+      </c>
+      <c r="F3" s="1">
         <v>471.21227118233702</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>24199.264253060501</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H3" s="1">
         <v>1478.0992456675899</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
         <v>92001.466114394294</v>
       </c>
-      <c r="I3" s="1">
+      <c r="K3" s="1">
         <v>56309.240982367999</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1461,25 +1621,31 @@
         <v>15</v>
       </c>
       <c r="D4" s="1">
+        <v>755.17097657026795</v>
+      </c>
+      <c r="E4" s="1">
+        <v>94.610650709218106</v>
+      </c>
+      <c r="F4" s="1">
         <v>748.97853731957196</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>35949.191362364101</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1">
         <v>1732.37581959659</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
         <v>95845.041376111796</v>
       </c>
-      <c r="I4" s="1">
+      <c r="K4" s="1">
         <v>57536.610010473501</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1490,25 +1656,31 @@
         <v>15</v>
       </c>
       <c r="D5" s="1">
+        <v>1575.42903839835</v>
+      </c>
+      <c r="E5" s="1">
+        <v>179.65668246493399</v>
+      </c>
+      <c r="F5" s="1">
         <v>1078.3247042913699</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>41385.655568557602</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>2051.42488497255</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
         <v>98117.404711791707</v>
       </c>
-      <c r="I5" s="1">
+      <c r="K5" s="1">
         <v>62314.640167808597</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1519,25 +1691,31 @@
         <v>15</v>
       </c>
       <c r="D6" s="1">
+        <v>3122.8871557037101</v>
+      </c>
+      <c r="E6" s="1">
+        <v>322.87235296295802</v>
+      </c>
+      <c r="F6" s="1">
         <v>2558.73855992571</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>51594.448092163497</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>2638.4901581972799</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>87.738182751532193</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>97210.410166385205</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>62045.2456145748</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1548,25 +1726,31 @@
         <v>15</v>
       </c>
       <c r="D7" s="1">
+        <v>4886.5307136194897</v>
+      </c>
+      <c r="E7" s="1">
+        <v>659.51659506351803</v>
+      </c>
+      <c r="F7" s="1">
         <v>3991.41740699092</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>60490.861182656197</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>3369.5524972613398</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>346.44176318324702</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>102926.86246957201</v>
       </c>
-      <c r="I7" s="1">
+      <c r="K7" s="1">
         <v>69846.065165256805</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1577,25 +1761,31 @@
         <v>15</v>
       </c>
       <c r="D8" s="1">
+        <v>5570.27773992108</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1048.8323760717601</v>
+      </c>
+      <c r="F8" s="1">
         <v>6795.5266068207902</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>68821.315490219204</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>5038.9446489478796</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>415.41063117379298</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>106206.729450813</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>70709.505373722495</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1606,25 +1796,31 @@
         <v>15</v>
       </c>
       <c r="D9" s="1">
+        <v>5840.7350319144998</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1484.6138884368199</v>
+      </c>
+      <c r="F9" s="1">
         <v>9220.5814719521404</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>75619.978243938502</v>
       </c>
-      <c r="F9" s="1">
+      <c r="H9" s="1">
         <v>7447.6092126076101</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>494.44171836475698</v>
       </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
         <v>103239.166063706</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>71121.424648442699</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1635,25 +1831,31 @@
         <v>15</v>
       </c>
       <c r="D10" s="1">
+        <v>6505.9976170607397</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2044.4521076507499</v>
+      </c>
+      <c r="F10" s="1">
         <v>16306.6233185903</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>70603.651477848602</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>8939.7834843230594</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>1322.1845081261999</v>
       </c>
-      <c r="H10" s="1">
+      <c r="J10" s="1">
         <v>100430.495382101</v>
       </c>
-      <c r="I10" s="1">
+      <c r="K10" s="1">
         <v>69780.673663897003</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1664,25 +1866,31 @@
         <v>15</v>
       </c>
       <c r="D11" s="1">
+        <v>6953.25625312998</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2622.3094113862699</v>
+      </c>
+      <c r="F11" s="1">
         <v>25666.444183610602</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
         <v>66406.970486713195</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="1">
         <v>7599.00745516807</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>4166.9852968654104</v>
       </c>
-      <c r="H11" s="1">
+      <c r="J11" s="1">
         <v>97810.253968283403</v>
       </c>
-      <c r="I11" s="1">
+      <c r="K11" s="1">
         <v>70084.460442772601</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1693,25 +1901,31 @@
         <v>15</v>
       </c>
       <c r="D12" s="1">
+        <v>6133.6922469671199</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2967.8893359683698</v>
+      </c>
+      <c r="F12" s="1">
         <v>31068.190418001301</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>50955.3786378765</v>
       </c>
-      <c r="F12" s="1">
+      <c r="H12" s="1">
         <v>3877.4105117599802</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>7121.4898909630801</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>80994.201656676494</v>
       </c>
-      <c r="I12" s="1">
+      <c r="K12" s="1">
         <v>57142.800067876698</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1722,25 +1936,31 @@
         <v>15</v>
       </c>
       <c r="D13" s="1">
+        <v>3924.1454093416501</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2530.46882220013</v>
+      </c>
+      <c r="F13" s="1">
         <v>28562.254090623501</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>36209.117019673598</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>1267.62332415935</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>9753.0242400838306</v>
       </c>
-      <c r="H13" s="1">
+      <c r="J13" s="1">
         <v>59077.403328476401</v>
       </c>
-      <c r="I13" s="1">
+      <c r="K13" s="1">
         <v>43155.481129965301</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1751,25 +1971,31 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
+        <v>3561.5253558592899</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2845.5314587020498</v>
+      </c>
+      <c r="F14" s="1">
         <v>33611.392735452697</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>31401.300423482498</v>
       </c>
-      <c r="F14" s="1">
+      <c r="H14" s="1">
         <v>217.89948573456999</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>15989.268430030899</v>
       </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
         <v>54816.379798116403</v>
       </c>
-      <c r="I14" s="1">
+      <c r="K14" s="1">
         <v>40189.834988506198</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1780,25 +2006,31 @@
         <v>15</v>
       </c>
       <c r="D15" s="1">
+        <v>2872.4362132907399</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2674.4782517745698</v>
+      </c>
+      <c r="F15" s="1">
         <v>31783.288336023099</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>23661.447827027299</v>
       </c>
-      <c r="F15" s="1">
+      <c r="H15" s="1">
         <v>102.968938857062</v>
       </c>
-      <c r="G15" s="1">
+      <c r="I15" s="1">
         <v>18356.632086485599</v>
       </c>
-      <c r="H15" s="1">
+      <c r="J15" s="1">
         <v>44040.047577108096</v>
       </c>
-      <c r="I15" s="1">
+      <c r="K15" s="1">
         <v>30742.587748637801</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1808,26 +2040,29 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
+        <v>26.6301551391632</v>
+      </c>
+      <c r="F16" s="1">
         <v>732.17669793488994</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>6903.3856171284597</v>
       </c>
-      <c r="F16" s="1">
+      <c r="H16" s="1">
         <v>1882.3261356478499</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
         <v>52459.133047528499</v>
       </c>
-      <c r="I16" s="1">
+      <c r="K16" s="1">
         <v>32341.602525145499</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1837,26 +2072,29 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
+        <v>48.451951991482403</v>
+      </c>
+      <c r="F17" s="1">
         <v>875.66547185091201</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>7572.9497652494201</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>2063.3176114873099</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
         <v>51487.6114650327</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>31226.703848296798</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1866,26 +2104,29 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
+        <v>135.01172415997999</v>
+      </c>
+      <c r="F18" s="1">
         <v>1522.39056592836</v>
       </c>
-      <c r="E18" s="1">
+      <c r="G18" s="1">
         <v>10728.119445366399</v>
       </c>
-      <c r="F18" s="1">
+      <c r="H18" s="1">
         <v>3182.9730794914199</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <v>53001.885335280604</v>
       </c>
-      <c r="I18" s="1">
+      <c r="K18" s="1">
         <v>31788.756570498401</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1895,26 +2136,29 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
+        <v>217.241820689961</v>
+      </c>
+      <c r="F19" s="1">
         <v>2386.2039972033499</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>13516.419112613899</v>
       </c>
-      <c r="F19" s="1">
+      <c r="H19" s="1">
         <v>4173.4852622846001</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
         <v>54004.563539681803</v>
       </c>
-      <c r="I19" s="1">
+      <c r="K19" s="1">
         <v>34295.186404271903</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1924,26 +2168,29 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
+        <v>335.29732433341002</v>
+      </c>
+      <c r="F20" s="1">
         <v>4904.3715053904198</v>
       </c>
-      <c r="E20" s="1">
+      <c r="G20" s="1">
         <v>18243.6701981068</v>
       </c>
-      <c r="F20" s="1">
+      <c r="H20" s="1">
         <v>5418.7089590147798</v>
       </c>
-      <c r="G20" s="1">
+      <c r="I20" s="1">
         <v>73.9401451264157</v>
       </c>
-      <c r="H20" s="1">
+      <c r="J20" s="1">
         <v>53494.462588376002</v>
       </c>
-      <c r="I20" s="1">
+      <c r="K20" s="1">
         <v>33905.283822597601</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1953,26 +2200,29 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
+        <v>714.973494068067</v>
+      </c>
+      <c r="F21" s="1">
         <v>7890.9428204744399</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>24637.452332464902</v>
       </c>
-      <c r="F21" s="1">
+      <c r="H21" s="1">
         <v>6607.8055836112298</v>
       </c>
-      <c r="G21" s="1">
+      <c r="I21" s="1">
         <v>319.383499940842</v>
       </c>
-      <c r="H21" s="1">
+      <c r="J21" s="1">
         <v>55783.629033686098</v>
       </c>
-      <c r="I21" s="1">
+      <c r="K21" s="1">
         <v>37632.573317415503</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -1982,26 +2232,29 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
+        <v>1335.2326714440201</v>
+      </c>
+      <c r="F22" s="1">
         <v>13193.520078261499</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>35868.234387963697</v>
       </c>
-      <c r="F22" s="1">
+      <c r="H22" s="1">
         <v>8590.7714098890792</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>342.058368473749</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
         <v>55531.209751856397</v>
       </c>
-      <c r="I22" s="1">
+      <c r="K22" s="1">
         <v>35983.486274115203</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2011,26 +2264,29 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
+        <v>2056.7785692744501</v>
+      </c>
+      <c r="F23" s="1">
         <v>18606.703142693601</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>47811.093394094598</v>
       </c>
-      <c r="F23" s="1">
+      <c r="H23" s="1">
         <v>10066.927515371901</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>421.23427726812002</v>
       </c>
-      <c r="H23" s="1">
+      <c r="J23" s="1">
         <v>52404.222916664497</v>
       </c>
-      <c r="I23" s="1">
+      <c r="K23" s="1">
         <v>34801.993057920001</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2040,26 +2296,29 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
+        <v>3182.7540512832602</v>
+      </c>
+      <c r="F24" s="1">
         <v>29286.974768860899</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>60906.428978592798</v>
       </c>
-      <c r="F24" s="1">
+      <c r="H24" s="1">
         <v>9740.8776702336709</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>1284.67521796611</v>
       </c>
-      <c r="H24" s="1">
+      <c r="J24" s="1">
         <v>48240.554310301603</v>
       </c>
-      <c r="I24" s="1">
+      <c r="K24" s="1">
         <v>32727.3315273232</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -2069,26 +2328,29 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
+        <v>4367.2525616008097</v>
+      </c>
+      <c r="F25" s="1">
         <v>41010.489145052699</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>68773.167936683807</v>
       </c>
-      <c r="F25" s="1">
+      <c r="H25" s="1">
         <v>7234.7744116886597</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>3492.81836113283</v>
       </c>
-      <c r="H25" s="1">
+      <c r="J25" s="1">
         <v>45361.153274361197</v>
       </c>
-      <c r="I25" s="1">
+      <c r="K25" s="1">
         <v>31382.510572155101</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2098,26 +2360,29 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
+        <v>4843.49979280359</v>
+      </c>
+      <c r="F26" s="1">
         <v>41885.195486218399</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>63162.831196373998</v>
       </c>
-      <c r="F26" s="1">
+      <c r="H26" s="1">
         <v>3193.9782544847899</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>5395.4809739491102</v>
       </c>
-      <c r="H26" s="1">
+      <c r="J26" s="1">
         <v>36008.780525071503</v>
       </c>
-      <c r="I26" s="1">
+      <c r="K26" s="1">
         <v>24306.229015712201</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -2127,26 +2392,29 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
+        <v>3508.92793544182</v>
+      </c>
+      <c r="F27" s="1">
         <v>30568.730726834699</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>43769.993921533402</v>
       </c>
-      <c r="F27" s="1">
+      <c r="H27" s="1">
         <v>919.29958004632294</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>6418.6206639030597</v>
       </c>
-      <c r="H27" s="1">
+      <c r="J27" s="1">
         <v>23844.600835253401</v>
       </c>
-      <c r="I27" s="1">
+      <c r="K27" s="1">
         <v>16784.8676980251</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -2156,26 +2424,29 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
+        <v>3173.3660850716601</v>
+      </c>
+      <c r="F28" s="1">
         <v>29682.2221039221</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>33925.402817990798</v>
       </c>
-      <c r="F28" s="1">
+      <c r="H28" s="1">
         <v>105.886084134353</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>9188.4349323497008</v>
       </c>
-      <c r="H28" s="1">
+      <c r="J28" s="1">
         <v>18875.3969379519</v>
       </c>
-      <c r="I28" s="1">
+      <c r="K28" s="1">
         <v>13090.894410745501</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -2185,22 +2456,25 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
+        <v>2556.4632611894599</v>
+      </c>
+      <c r="F29" s="1">
         <v>22499.177480744602</v>
       </c>
-      <c r="E29" s="1">
+      <c r="G29" s="1">
         <v>21763.281474445499</v>
       </c>
-      <c r="F29" s="1">
+      <c r="H29" s="1">
         <v>37.156910532311599</v>
       </c>
-      <c r="G29" s="1">
+      <c r="I29" s="1">
         <v>8750.47364491589</v>
       </c>
-      <c r="H29" s="1">
+      <c r="J29" s="1">
         <v>12144.0385964947</v>
       </c>
-      <c r="I29" s="1">
+      <c r="K29" s="1">
         <v>7989.5474402997597</v>
       </c>
     </row>
@@ -2211,18 +2485,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F9C405-CC78-DE47-80BA-51DD73EFCA1A}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -2233,25 +2509,31 @@
         <v>21</v>
       </c>
       <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2262,25 +2544,31 @@
         <v>15</v>
       </c>
       <c r="D2" s="1">
+        <v>59.804399829096397</v>
+      </c>
+      <c r="E2" s="1">
+        <v>39.558076580761004</v>
+      </c>
+      <c r="F2" s="1">
         <v>642.129110645482</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>45101.689759668297</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1">
         <v>2523.74999829432</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
         <v>138801.978834651</v>
       </c>
-      <c r="I2" s="1">
+      <c r="K2" s="1">
         <v>79621.9456363192</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2291,25 +2579,31 @@
         <v>15</v>
       </c>
       <c r="D3" s="1">
+        <v>338.75419398620102</v>
+      </c>
+      <c r="E3" s="1">
+        <v>65.571164526666095</v>
+      </c>
+      <c r="F3" s="1">
         <v>835.24767500852295</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>64924.075297868498</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H3" s="1">
         <v>3002.3680942698702</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
         <v>134334.177423841</v>
       </c>
-      <c r="I3" s="1">
+      <c r="K3" s="1">
         <v>80433.486807937195</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2320,25 +2614,31 @@
         <v>15</v>
       </c>
       <c r="D4" s="1">
+        <v>1099.1886487762899</v>
+      </c>
+      <c r="E4" s="1">
+        <v>148.46584721539801</v>
+      </c>
+      <c r="F4" s="1">
         <v>1167.13932798873</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>81735.535434642006</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1">
         <v>3660.9913132224701</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
         <v>135290.46076181901</v>
       </c>
-      <c r="I4" s="1">
+      <c r="K4" s="1">
         <v>84230.089263609596</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2349,25 +2649,31 @@
         <v>15</v>
       </c>
       <c r="D5" s="1">
+        <v>2160.8757418802202</v>
+      </c>
+      <c r="E5" s="1">
+        <v>271.695847512353</v>
+      </c>
+      <c r="F5" s="1">
         <v>1684.4540816368401</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>100870.669712984</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>4654.6955970973604</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
         <v>138678.74731181099</v>
       </c>
-      <c r="I5" s="1">
+      <c r="K5" s="1">
         <v>86067.449018426298</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2378,25 +2684,31 @@
         <v>15</v>
       </c>
       <c r="D6" s="1">
+        <v>4034.4713182320102</v>
+      </c>
+      <c r="E6" s="1">
+        <v>478.803499594897</v>
+      </c>
+      <c r="F6" s="1">
         <v>3726.8103490562698</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>111586.798374929</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>5163.1622850513504</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>339.387898639561</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>136953.78567725999</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>89640.730596265406</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2407,25 +2719,31 @@
         <v>15</v>
       </c>
       <c r="D7" s="1">
+        <v>6448.6304587740196</v>
+      </c>
+      <c r="E7" s="1">
+        <v>935.16127254529101</v>
+      </c>
+      <c r="F7" s="1">
         <v>6962.4320982106001</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>140738.44331002099</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>6694.3701977393903</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>838.63762340512596</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>145904.23741587199</v>
       </c>
-      <c r="I7" s="1">
+      <c r="K7" s="1">
         <v>93555.262635121806</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2436,25 +2754,31 @@
         <v>15</v>
       </c>
       <c r="D8" s="1">
+        <v>7539.1352370761797</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1409.87727722094</v>
+      </c>
+      <c r="F8" s="1">
         <v>10496.916387537</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>144889.84020291499</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>9029.3727817545896</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>1030.3448775004799</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>146698.36388370799</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>98613.814029934598</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2465,25 +2789,31 @@
         <v>15</v>
       </c>
       <c r="D9" s="1">
+        <v>7783.4596160726596</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1950.31315103461</v>
+      </c>
+      <c r="F9" s="1">
         <v>17270.020826055301</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>144759.89546308201</v>
       </c>
-      <c r="F9" s="1">
+      <c r="H9" s="1">
         <v>12517.466134808101</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>1405.4112792992701</v>
       </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
         <v>139865.58457303501</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>97260.106005538793</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -2494,25 +2824,31 @@
         <v>15</v>
       </c>
       <c r="D10" s="1">
+        <v>8682.5409281786397</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2659.8364690378298</v>
+      </c>
+      <c r="F10" s="1">
         <v>26222.9007885106</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>137165.71236874399</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>12913.7106924167</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>3133.34653567033</v>
       </c>
-      <c r="H10" s="1">
+      <c r="J10" s="1">
         <v>138761.047798849</v>
       </c>
-      <c r="I10" s="1">
+      <c r="K10" s="1">
         <v>95299.347541525305</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2523,25 +2859,31 @@
         <v>15</v>
       </c>
       <c r="D11" s="1">
+        <v>9419.7461775662505</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3469.3239358794799</v>
+      </c>
+      <c r="F11" s="1">
         <v>42073.098996386798</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
         <v>128392.78024285</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="1">
         <v>11900.0316725886</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>7203.4588355820897</v>
       </c>
-      <c r="H11" s="1">
+      <c r="J11" s="1">
         <v>142257.93824029199</v>
       </c>
-      <c r="I11" s="1">
+      <c r="K11" s="1">
         <v>92332.258729937996</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -2552,25 +2894,31 @@
         <v>15</v>
       </c>
       <c r="D12" s="1">
+        <v>8392.0729819998396</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4016.4858490390998</v>
+      </c>
+      <c r="F12" s="1">
         <v>45614.958709516002</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>100310.28210771301</v>
       </c>
-      <c r="F12" s="1">
+      <c r="H12" s="1">
         <v>7616.1550117172501</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>12288.5092118624</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>118913.54042939701</v>
       </c>
-      <c r="I12" s="1">
+      <c r="K12" s="1">
         <v>79845.600196532905</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2581,25 +2929,31 @@
         <v>15</v>
       </c>
       <c r="D13" s="1">
+        <v>5605.4318767363702</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3581.1551481731099</v>
+      </c>
+      <c r="F13" s="1">
         <v>44305.570506391399</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>57311.304626032499</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>2187.2252600194101</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>17006.707577093199</v>
       </c>
-      <c r="H13" s="1">
+      <c r="J13" s="1">
         <v>84294.887451215094</v>
       </c>
-      <c r="I13" s="1">
+      <c r="K13" s="1">
         <v>58632.261798236999</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -2610,25 +2964,31 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
+        <v>5646.2836974170305</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4613.8355980015103</v>
+      </c>
+      <c r="F14" s="1">
         <v>49483.565136865298</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>49737.344193223798</v>
       </c>
-      <c r="F14" s="1">
+      <c r="H14" s="1">
         <v>589.961836999159</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>26251.522138160799</v>
       </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
         <v>78378.019836771899</v>
       </c>
-      <c r="I14" s="1">
+      <c r="K14" s="1">
         <v>55905.972149341003</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -2639,25 +2999,31 @@
         <v>15</v>
       </c>
       <c r="D15" s="1">
+        <v>4837.96788784605</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4512.5928895033103</v>
+      </c>
+      <c r="F15" s="1">
         <v>50726.232449147203</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>35934.197858170097</v>
       </c>
-      <c r="F15" s="1">
+      <c r="H15" s="1">
         <v>252.87416136956799</v>
       </c>
-      <c r="G15" s="1">
+      <c r="I15" s="1">
         <v>29294.222935033202</v>
       </c>
-      <c r="H15" s="1">
+      <c r="J15" s="1">
         <v>60698.698858546697</v>
       </c>
-      <c r="I15" s="1">
+      <c r="K15" s="1">
         <v>46098.252192666499</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2667,26 +3033,29 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
+        <v>47.422020467506997</v>
+      </c>
+      <c r="F16" s="1">
         <v>1347.3945715340301</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>15262.467575066201</v>
       </c>
-      <c r="F16" s="1">
+      <c r="H16" s="1">
         <v>3799.4856851865602</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
         <v>79932.820095374904</v>
       </c>
-      <c r="I16" s="1">
+      <c r="K16" s="1">
         <v>47283.987962690298</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2696,26 +3065,29 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
+        <v>78.367669383549995</v>
+      </c>
+      <c r="F17" s="1">
         <v>1649.9146067435099</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>17262.374967923501</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>4799.7685902288704</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
         <v>75294.311268587902</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>47088.315859173301</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -2725,26 +3097,29 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
+        <v>208.42688819551</v>
+      </c>
+      <c r="F18" s="1">
         <v>2371.2075734478499</v>
       </c>
-      <c r="E18" s="1">
+      <c r="G18" s="1">
         <v>22088.826810386101</v>
       </c>
-      <c r="F18" s="1">
+      <c r="H18" s="1">
         <v>6413.2160890507603</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <v>74562.117488012795</v>
       </c>
-      <c r="I18" s="1">
+      <c r="K18" s="1">
         <v>48856.6953063236</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2754,26 +3129,29 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
+        <v>317.170981278905</v>
+      </c>
+      <c r="F19" s="1">
         <v>3615.3864966910901</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>28666.023924118301</v>
       </c>
-      <c r="F19" s="1">
+      <c r="H19" s="1">
         <v>8418.2629535505694</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
         <v>77561.278356379102</v>
       </c>
-      <c r="I19" s="1">
+      <c r="K19" s="1">
         <v>49788.700798170998</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2783,26 +3161,29 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
+        <v>471.48268342005099</v>
+      </c>
+      <c r="F20" s="1">
         <v>6517.7431013639898</v>
       </c>
-      <c r="E20" s="1">
+      <c r="G20" s="1">
         <v>33451.674914397699</v>
       </c>
-      <c r="F20" s="1">
+      <c r="H20" s="1">
         <v>9649.9671734145595</v>
       </c>
-      <c r="G20" s="1">
+      <c r="I20" s="1">
         <v>304.33648533112603</v>
       </c>
-      <c r="H20" s="1">
+      <c r="J20" s="1">
         <v>75885.270495522505</v>
       </c>
-      <c r="I20" s="1">
+      <c r="K20" s="1">
         <v>51466.440542918303</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -2812,26 +3193,29 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
+        <v>999.92422027439795</v>
+      </c>
+      <c r="F21" s="1">
         <v>11825.4136507613</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>50711.385527780702</v>
       </c>
-      <c r="F21" s="1">
+      <c r="H21" s="1">
         <v>12117.2445017883</v>
       </c>
-      <c r="G21" s="1">
+      <c r="I21" s="1">
         <v>730.47820433884601</v>
       </c>
-      <c r="H21" s="1">
+      <c r="J21" s="1">
         <v>79983.308623345103</v>
       </c>
-      <c r="I21" s="1">
+      <c r="K21" s="1">
         <v>53178.667848150399</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2841,26 +3225,29 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
+        <v>1805.2418194035799</v>
+      </c>
+      <c r="F22" s="1">
         <v>18114.1294362927</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>62394.887720340397</v>
       </c>
-      <c r="F22" s="1">
+      <c r="H22" s="1">
         <v>13849.6866874922</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>886.98284525974498</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
         <v>77694.023051982906</v>
       </c>
-      <c r="I22" s="1">
+      <c r="K22" s="1">
         <v>52582.551384206199</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -2870,26 +3257,29 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
+        <v>2671.2234148494899</v>
+      </c>
+      <c r="F23" s="1">
         <v>28165.924911537699</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>79332.442986173002</v>
       </c>
-      <c r="F23" s="1">
+      <c r="H23" s="1">
         <v>17086.024151701298</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>1245.8545953625801</v>
       </c>
-      <c r="H23" s="1">
+      <c r="J23" s="1">
         <v>71221.094453531696</v>
       </c>
-      <c r="I23" s="1">
+      <c r="K23" s="1">
         <v>50016.900051043202</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2899,26 +3289,29 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
+        <v>4084.6148100093701</v>
+      </c>
+      <c r="F24" s="1">
         <v>39976.591433394096</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>93784.351040393201</v>
       </c>
-      <c r="F24" s="1">
+      <c r="H24" s="1">
         <v>15428.0057651596</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>2838.05794219465</v>
       </c>
-      <c r="H24" s="1">
+      <c r="J24" s="1">
         <v>67354.644457613598</v>
       </c>
-      <c r="I24" s="1">
+      <c r="K24" s="1">
         <v>45813.211646001699</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -2928,26 +3321,29 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
+        <v>5609.2200905805203</v>
+      </c>
+      <c r="F25" s="1">
         <v>59567.671669830503</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>112349.387242595</v>
       </c>
-      <c r="F25" s="1">
+      <c r="H25" s="1">
         <v>12945.5492635112</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>6364.5755757529396</v>
       </c>
-      <c r="H25" s="1">
+      <c r="J25" s="1">
         <v>67257.735444433099</v>
       </c>
-      <c r="I25" s="1">
+      <c r="K25" s="1">
         <v>43471.406191182097</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -2957,26 +3353,29 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
+        <v>6253.7763322601904</v>
+      </c>
+      <c r="F26" s="1">
         <v>56711.031005466997</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>98582.7432954994</v>
       </c>
-      <c r="F26" s="1">
+      <c r="H26" s="1">
         <v>7729.5594035261802</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>9780.1680736949093</v>
       </c>
-      <c r="H26" s="1">
+      <c r="J26" s="1">
         <v>53498.621752128704</v>
       </c>
-      <c r="I26" s="1">
+      <c r="K26" s="1">
         <v>36043.679827715503</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -2986,26 +3385,29 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
+        <v>4532.96721031982</v>
+      </c>
+      <c r="F27" s="1">
         <v>44998.082220413002</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>62034.502835804902</v>
       </c>
-      <c r="F27" s="1">
+      <c r="H27" s="1">
         <v>1873.36497002801</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>11852.898192500599</v>
       </c>
-      <c r="H27" s="1">
+      <c r="J27" s="1">
         <v>34551.895088555597</v>
       </c>
-      <c r="I27" s="1">
+      <c r="K27" s="1">
         <v>23867.2419793607</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -3015,26 +3417,29 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
+        <v>4422.61849416733</v>
+      </c>
+      <c r="F28" s="1">
         <v>40759.000567518902</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>47209.029960939399</v>
       </c>
-      <c r="F28" s="1">
+      <c r="H28" s="1">
         <v>307.24312553894498</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>16327.443986461099</v>
       </c>
-      <c r="H28" s="1">
+      <c r="J28" s="1">
         <v>27665.411221903702</v>
       </c>
-      <c r="I28" s="1">
+      <c r="K28" s="1">
         <v>19303.870779180601</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -3044,22 +3449,25 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
+        <v>3648.8893564674299</v>
+      </c>
+      <c r="F29" s="1">
         <v>32994.459846837803</v>
       </c>
-      <c r="E29" s="1">
+      <c r="G29" s="1">
         <v>29950.4557205399</v>
       </c>
-      <c r="F29" s="1">
+      <c r="H29" s="1">
         <v>101.43299458342101</v>
       </c>
-      <c r="G29" s="1">
+      <c r="I29" s="1">
         <v>15031.7875034074</v>
       </c>
-      <c r="H29" s="1">
+      <c r="J29" s="1">
         <v>16842.1456445771</v>
       </c>
-      <c r="I29" s="1">
+      <c r="K29" s="1">
         <v>12626.1323890277</v>
       </c>
     </row>
